--- a/grid_raw_data.xlsx
+++ b/grid_raw_data.xlsx
@@ -1,132 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -417,7 +288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,7 +705,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46187.63463058524</v>
+        <v>46187.63463059028</v>
       </c>
       <c r="B17" t="n">
         <v>49.8</v>
@@ -854,6 +725,931 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>2026-06-14T09:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46187.97785517361</v>
+      </c>
+      <c r="B18" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D18" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E18" t="n">
+        <v>640</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46187.97792106481</v>
+      </c>
+      <c r="B19" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>640</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46187.97796973379</v>
+      </c>
+      <c r="B20" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D20" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E20" t="n">
+        <v>640</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46187.9780078125</v>
+      </c>
+      <c r="B21" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E21" t="n">
+        <v>640</v>
+      </c>
+      <c r="F21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46187.97803653935</v>
+      </c>
+      <c r="B22" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D22" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E22" t="n">
+        <v>640</v>
+      </c>
+      <c r="F22" t="n">
+        <v>33</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46187.97811140047</v>
+      </c>
+      <c r="B23" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D23" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E23" t="n">
+        <v>640</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46187.97812715278</v>
+      </c>
+      <c r="B24" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D24" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E24" t="n">
+        <v>640</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46187.9781362037</v>
+      </c>
+      <c r="B25" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D25" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E25" t="n">
+        <v>640</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46187.97814140046</v>
+      </c>
+      <c r="B26" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D26" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E26" t="n">
+        <v>640</v>
+      </c>
+      <c r="F26" t="n">
+        <v>33</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46187.97814619213</v>
+      </c>
+      <c r="B27" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E27" t="n">
+        <v>640</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46187.97816454861</v>
+      </c>
+      <c r="B28" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D28" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E28" t="n">
+        <v>640</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46187.97817109954</v>
+      </c>
+      <c r="B29" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D29" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E29" t="n">
+        <v>640</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46187.97817450231</v>
+      </c>
+      <c r="B30" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D30" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E30" t="n">
+        <v>640</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46187.97818151621</v>
+      </c>
+      <c r="B31" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D31" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E31" t="n">
+        <v>640</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46187.97818725694</v>
+      </c>
+      <c r="B32" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D32" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E32" t="n">
+        <v>640</v>
+      </c>
+      <c r="F32" t="n">
+        <v>33</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46187.97819641203</v>
+      </c>
+      <c r="B33" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D33" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E33" t="n">
+        <v>640</v>
+      </c>
+      <c r="F33" t="n">
+        <v>33</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46187.97820643518</v>
+      </c>
+      <c r="B34" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D34" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E34" t="n">
+        <v>640</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46187.97821831019</v>
+      </c>
+      <c r="B35" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D35" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E35" t="n">
+        <v>640</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46187.97822979167</v>
+      </c>
+      <c r="B36" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D36" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E36" t="n">
+        <v>640</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46187.97823730324</v>
+      </c>
+      <c r="B37" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D37" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E37" t="n">
+        <v>640</v>
+      </c>
+      <c r="F37" t="n">
+        <v>33</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46187.97824502315</v>
+      </c>
+      <c r="B38" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>900</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HTTPSConnectionPool(host='api.electricitymaps.com', port=443): Read timed out. (read timeout=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46187.97824755787</v>
+      </c>
+      <c r="B39" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D39" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E39" t="n">
+        <v>640</v>
+      </c>
+      <c r="F39" t="n">
+        <v>33</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46187.97825081019</v>
+      </c>
+      <c r="B40" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D40" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E40" t="n">
+        <v>640</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46187.97826175926</v>
+      </c>
+      <c r="B41" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D41" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E41" t="n">
+        <v>640</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46187.97826311343</v>
+      </c>
+      <c r="B42" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C42" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D42" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E42" t="n">
+        <v>640</v>
+      </c>
+      <c r="F42" t="n">
+        <v>33</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46187.97827950231</v>
+      </c>
+      <c r="B43" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D43" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E43" t="n">
+        <v>640</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46187.97828248842</v>
+      </c>
+      <c r="B44" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C44" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D44" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E44" t="n">
+        <v>640</v>
+      </c>
+      <c r="F44" t="n">
+        <v>33</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46187.97828394676</v>
+      </c>
+      <c r="B45" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D45" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E45" t="n">
+        <v>640</v>
+      </c>
+      <c r="F45" t="n">
+        <v>33</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46187.97828553241</v>
+      </c>
+      <c r="B46" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D46" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E46" t="n">
+        <v>640</v>
+      </c>
+      <c r="F46" t="n">
+        <v>33</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46187.97830952546</v>
+      </c>
+      <c r="B47" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D47" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E47" t="n">
+        <v>640</v>
+      </c>
+      <c r="F47" t="n">
+        <v>33</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46187.97832021991</v>
+      </c>
+      <c r="B48" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C48" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D48" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E48" t="n">
+        <v>640</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46187.97832302083</v>
+      </c>
+      <c r="B49" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C49" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D49" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E49" t="n">
+        <v>640</v>
+      </c>
+      <c r="F49" t="n">
+        <v>33</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46187.97832372685</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C50" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D50" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E50" t="n">
+        <v>640</v>
+      </c>
+      <c r="F50" t="n">
+        <v>33</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46187.97833856481</v>
+      </c>
+      <c r="B51" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C51" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D51" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E51" t="n">
+        <v>640</v>
+      </c>
+      <c r="F51" t="n">
+        <v>33</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46187.97836354167</v>
+      </c>
+      <c r="B52" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C52" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D52" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E52" t="n">
+        <v>640</v>
+      </c>
+      <c r="F52" t="n">
+        <v>33</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46187.97836855324</v>
+      </c>
+      <c r="B53" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C53" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D53" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E53" t="n">
+        <v>640</v>
+      </c>
+      <c r="F53" t="n">
+        <v>33</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46187.97837018764</v>
+      </c>
+      <c r="B54" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="C54" t="n">
+        <v>77027.64646434024</v>
+      </c>
+      <c r="D54" t="n">
+        <v>80879.03</v>
+      </c>
+      <c r="E54" t="n">
+        <v>640</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00.000Z</t>
         </is>
       </c>
     </row>
